--- a/data/skills.xlsx
+++ b/data/skills.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,7 +442,7 @@
         <v>神扑</v>
       </c>
       <c r="C2" t="str">
-        <v>提升扑救成功率</v>
+        <v>关键时刻扑出必进球</v>
       </c>
       <c r="D2" t="str">
         <v>passive</v>
@@ -477,7 +477,7 @@
         <v>飞铲</v>
       </c>
       <c r="C3" t="str">
-        <v>提升铲断能力</v>
+        <v>凶猛的铲断技术</v>
       </c>
       <c r="D3" t="str">
         <v>passive</v>
@@ -512,7 +512,7 @@
         <v>暴力射门</v>
       </c>
       <c r="C4" t="str">
-        <v>提升射门威力</v>
+        <v>蓄力射出势大力沉的射门</v>
       </c>
       <c r="D4" t="str">
         <v>active</v>
@@ -547,7 +547,7 @@
         <v>灵巧过人</v>
       </c>
       <c r="C5" t="str">
-        <v>提升突破成功率</v>
+        <v>闪转腾挪突破防线</v>
       </c>
       <c r="D5" t="str">
         <v>active</v>
@@ -582,7 +582,7 @@
         <v>致命直塞</v>
       </c>
       <c r="C6" t="str">
-        <v>提升传球精准度</v>
+        <v>一脚精准直塞撕裂防线</v>
       </c>
       <c r="D6" t="str">
         <v>active</v>
@@ -617,7 +617,7 @@
         <v>任意球大师</v>
       </c>
       <c r="C7" t="str">
-        <v>获得额外定位球机会</v>
+        <v>定位球直挂死角</v>
       </c>
       <c r="D7" t="str">
         <v>active</v>
@@ -644,9 +644,219 @@
         <v>5</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>skill_iron_wall</v>
+      </c>
+      <c r="B8" t="str">
+        <v>铁壁防守</v>
+      </c>
+      <c r="C8" t="str">
+        <v>铜墙铁壁固若金汤</v>
+      </c>
+      <c r="D8" t="str">
+        <v>passive</v>
+      </c>
+      <c r="E8" t="str">
+        <v>self</v>
+      </c>
+      <c r="F8" t="str">
+        <v>buff_defense</v>
+      </c>
+      <c r="G8">
+        <v>18</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
+        <v>on_tackle</v>
+      </c>
+      <c r="J8" t="str">
+        <v>anim_iron_wall</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>skill_thunder</v>
+      </c>
+      <c r="B9" t="str">
+        <v>雷霆射门</v>
+      </c>
+      <c r="C9" t="str">
+        <v>如雷霆般的暴力远射</v>
+      </c>
+      <c r="D9" t="str">
+        <v>active</v>
+      </c>
+      <c r="E9" t="str">
+        <v>self</v>
+      </c>
+      <c r="F9" t="str">
+        <v>buff_attack</v>
+      </c>
+      <c r="G9">
+        <v>25</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="str">
+        <v>on_shot</v>
+      </c>
+      <c r="J9" t="str">
+        <v>anim_thunder</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>skill_shadow</v>
+      </c>
+      <c r="B10" t="str">
+        <v>鬼影步法</v>
+      </c>
+      <c r="C10" t="str">
+        <v>身法诡异让对手无法捕捉</v>
+      </c>
+      <c r="D10" t="str">
+        <v>active</v>
+      </c>
+      <c r="E10" t="str">
+        <v>self</v>
+      </c>
+      <c r="F10" t="str">
+        <v>buff_speed</v>
+      </c>
+      <c r="G10">
+        <v>22</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="str">
+        <v>on_pass</v>
+      </c>
+      <c r="J10" t="str">
+        <v>anim_shadow</v>
+      </c>
+      <c r="K10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>skill_eagle</v>
+      </c>
+      <c r="B11" t="str">
+        <v>鹰眼长传</v>
+      </c>
+      <c r="C11" t="str">
+        <v>精准的长距离传球找到队友</v>
+      </c>
+      <c r="D11" t="str">
+        <v>active</v>
+      </c>
+      <c r="E11" t="str">
+        <v>team</v>
+      </c>
+      <c r="F11" t="str">
+        <v>buff_technique</v>
+      </c>
+      <c r="G11">
+        <v>18</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" t="str">
+        <v>on_pass</v>
+      </c>
+      <c r="J11" t="str">
+        <v>anim_eagle</v>
+      </c>
+      <c r="K11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>skill_dragon</v>
+      </c>
+      <c r="B12" t="str">
+        <v>龙门飞渡</v>
+      </c>
+      <c r="C12" t="str">
+        <v>化身蛟龙飞扑封堵一切射门</v>
+      </c>
+      <c r="D12" t="str">
+        <v>active</v>
+      </c>
+      <c r="E12" t="str">
+        <v>self</v>
+      </c>
+      <c r="F12" t="str">
+        <v>buff_defense</v>
+      </c>
+      <c r="G12">
+        <v>30</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" t="str">
+        <v>on_shot</v>
+      </c>
+      <c r="J12" t="str">
+        <v>anim_dragon</v>
+      </c>
+      <c r="K12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>skill_tiger</v>
+      </c>
+      <c r="B13" t="str">
+        <v>猛虎断球</v>
+      </c>
+      <c r="C13" t="str">
+        <v>如猛虎下山般凶猛断球</v>
+      </c>
+      <c r="D13" t="str">
+        <v>active</v>
+      </c>
+      <c r="E13" t="str">
+        <v>self</v>
+      </c>
+      <c r="F13" t="str">
+        <v>buff_defense</v>
+      </c>
+      <c r="G13">
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" t="str">
+        <v>on_tackle</v>
+      </c>
+      <c r="J13" t="str">
+        <v>anim_tiger</v>
+      </c>
+      <c r="K13">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K13"/>
   </ignoredErrors>
 </worksheet>
 </file>